--- a/docs/entregables/Plan-de-pruebas-completo.xlsx
+++ b/docs/entregables/Plan-de-pruebas-completo.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="L56" s="18" t="inlineStr"/>
     </row>
-    <row r="57" ht="36" customHeight="1">
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
         <is>
           <t>P05</t>
@@ -4260,24 +4260,25 @@
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>SEGURIDAD: exposición de datos personales por cédula</t>
+          <t>El autocompletado por cédula exige un segundo dato</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>Una cédula que compró antes</t>
+          <t>Una cédula que compró antes, con su correo registrado</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>1. Sin sesión, consultar la búsqueda de clientes por cédula
-2. Revisar todos los campos que devuelve
-3. Probar con dos o tres cédulas consecutivas</t>
+          <t>1. Sin sesión, consultar la búsqueda de clientes enviando SÓLO la cédula
+2. Repetir enviando la cédula y el correo correcto
+3. Repetir enviando la cédula y un correo equivocado
+4. Repetir más de diez veces seguidas en menos de un minuto</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>HALLAZGO ESPERADO: hoy devuelve nombre, apellido, correo, teléfono, dirección, ciudad y coordenadas de cualquier cliente, sin autenticación. Documentar el alcance exacto y escalarlo.</t>
+          <t>Con la cédula sola no devuelve nada. Con la cédula y el correo correcto devuelve los datos para autocompletar. Con el correo equivocado no devuelve nada, igual que si la cédula no existiera. A partir de la undécima consulta en un minuto responde «demasiadas solicitudes».</t>
         </is>
       </c>
       <c r="H57" s="16" t="inlineStr">
